--- a/data/trans_dic/P39A2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,61; 75,02</t>
+          <t>67,29; 75,55</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,62; 77,16</t>
+          <t>71,6; 77,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,86; 75,44</t>
+          <t>70,8; 75,54</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,38; 82,79</t>
+          <t>71,29; 84,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,09; 76,38</t>
+          <t>61,32; 75,85</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,4; 77,14</t>
+          <t>67,36; 76,78</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,72; 72,43</t>
+          <t>63,82; 72,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,21; 66,93</t>
+          <t>60,05; 66,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>63,26; 68,46</t>
+          <t>62,93; 68,41</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,63; 80,05</t>
+          <t>70,53; 79,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,89; 73,97</t>
+          <t>63,9; 73,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>68,1; 74,98</t>
+          <t>67,95; 74,7</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que sentirse débil mareado o a punto de desmayarse es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 90,01%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>280994; 316473</t>
+          <t>283859; 318696</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>430925; 464205</t>
+          <t>430796; 463246</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>725196; 772095</t>
+          <t>724605; 773134</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1527506; 1771753</t>
+          <t>1525621; 1808535</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1256281; 1570839</t>
+          <t>1261187; 1560019</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2828423; 3237314</t>
+          <t>2827024; 3222312</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>393271; 447015</t>
+          <t>393882; 444856</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>378439; 420688</t>
+          <t>377437; 420010</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>788075; 852854</t>
+          <t>783970; 852228</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2245207; 2544782</t>
+          <t>2242146; 2523972</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2099795; 2431142</t>
+          <t>2100223; 2418781</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4403094; 4848260</t>
+          <t>4393400; 4829996</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A2_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P39A2_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>71,34%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>67,29; 75,55</t>
+          <t>66,43; 74,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>71,6; 77,0</t>
+          <t>71,9; 77,35</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>70,8; 75,54</t>
+          <t>70,73; 75,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>66,33%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>71,29; 84,51</t>
+          <t>69,37; 73,96</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>61,32; 75,85</t>
+          <t>64,28; 68,31</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67,36; 76,78</t>
+          <t>67,73; 70,34</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>68,43%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>63,47%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>65,93%</t>
+          <t>66,05%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63,82; 72,08</t>
+          <t>65,14; 72,88</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,05; 66,82</t>
+          <t>59,81; 66,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>62,93; 68,41</t>
+          <t>63,44; 68,7</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>70,95%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>70,53; 79,39</t>
+          <t>69,04; 72,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,9; 73,59</t>
+          <t>65,79; 68,59</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67,95; 74,7</t>
+          <t>67,99; 70,1</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>300935</t>
+          <t>327979</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>447901</t>
+          <t>488484</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>748836</t>
+          <t>816463</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>283859; 318696</t>
+          <t>308105; 346126</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>430796; 463246</t>
+          <t>470180; 505800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>724605; 773134</t>
+          <t>790570; 840342</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1610725</t>
+          <t>1467449</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1395150</t>
+          <t>1323531</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3005874</t>
+          <t>2790981</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1525621; 1808535</t>
+          <t>1421675; 1515689</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1261187; 1560019</t>
+          <t>1282733; 1363191</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2827024; 3222312</t>
+          <t>2739420; 2844980</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>422367</t>
+          <t>468168</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>398921</t>
+          <t>439041</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>821289</t>
+          <t>907209</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>393882; 444856</t>
+          <t>441182; 493620</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>377437; 420010</t>
+          <t>416471; 463391</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>783970; 852228</t>
+          <t>871411; 943642</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2334027</t>
+          <t>2263597</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2241972</t>
+          <t>2251058</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4575999</t>
+          <t>4514653</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2242146; 2523972</t>
+          <t>2202800; 2316661</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2100223; 2418781</t>
+          <t>2201279; 2294760</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4393400; 4829996</t>
+          <t>4443978; 4581937</t>
         </is>
       </c>
     </row>
